--- a/SmartVoc-Fehler-und-Aenderungen.xlsx
+++ b/SmartVoc-Fehler-und-Aenderungen.xlsx
@@ -7,7 +7,7 @@
   </sheets>
   <definedNames>
     <definedName name="Typ">'Listen und Anleitung'!$A$2:$A$7</definedName>
-    <definedName name="Bereich">'Listen und Anleitung'!$B$2:$B$13</definedName>
+    <definedName name="Bereich">'Listen und Anleitung'!$B$2:$B$14</definedName>
     <definedName name="Schwere">'Listen und Anleitung'!$C$2:$C$6</definedName>
     <definedName name="Prioritaet">'Listen und Anleitung'!$D$2:$D$5</definedName>
     <definedName name="Status">'Listen und Anleitung'!$E$2:$E$8</definedName>
@@ -678,344 +678,1168 @@
     <row r="9">
       <c r="A9" s="3" t="str">
         <f>IF($F9="","","SV-"&amp;TEXT(ROW()-1,"000"))</f>
-        <v/>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
+        <v>SV-008</v>
+      </c>
+      <c r="B9" s="4">
+        <v>46274</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martin</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aufgabe</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plan und Kauf</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grundsatzentscheid: Freemium in 1.0 oder erst in 1.1</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build 1.0 (2) liegt in der Beta-Prüfung und stempelt jeden Nutzer beim ersten Start auf «pro» (plan.ts, PLAN_NEU). Freemium samt Kauf, Grenzen, Upgrade-Weg und Wiederherstellen ist nirgends gebaut.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bewusst entscheiden: 1.0 wie gebaut veröffentlichen und Pro in 1.1 nachziehen, oder 1.0 zurückhalten, bis der Kauf steht.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.0 (2)</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blocker</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sofort</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neu</t>
+        </is>
+      </c>
       <c r="M9" s="3"/>
-      <c r="N9" s="2"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Der Bestandsschutz in plan.ts wurde genau für den ersten Weg gebaut: wer heute stempelt, behält Pro für immer. Alle folgenden Einträge hängen an dieser Entscheidung.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="str">
         <f>IF($F10="","","SV-"&amp;TEXT(ROW()-1,"000"))</f>
-        <v/>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
+        <v>SV-009</v>
+      </c>
+      <c r="B10" s="4">
+        <v>46274</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martin</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aufgabe</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plan und Kauf</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Einen einzigen Bezahl-Schnitt festlegen — heute stehen zwei im Code</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">plan.ts: gratis = 1 eigene Liste JE SPRACHE, 40 Wörter je Liste, kein Teilen. premium.ts beschreibt einen ganz anderen Schnitt: gratis = Eintippen, Einfügen, CSV/Excel, OCR und Sync; kostenpflichtig = die KI-Funktionen. Beide stehen nebeneinander, keiner ist verdrahtet.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ein Schnitt an einer Stelle: 1 persönliche Liste INSGESAMT, 50 eigene Wörter, Kern-FSRS und Übungsplan frei, keine Werbung. GRENZEN in plan.ts anpassen, premium.ts auflösen oder angleichen.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alle</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Schwer</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vor Release</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neu</t>
+        </is>
+      </c>
       <c r="M10" s="3"/>
-      <c r="N10" s="2"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solange zwei Beschreibungen im Code stehen, baut jeder, der eine davon liest, das Falsche.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="str">
         <f>IF($F11="","","SV-"&amp;TEXT(ROW()-1,"000"))</f>
-        <v/>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
+        <v>SV-010</v>
+      </c>
+      <c r="B11" s="4">
+        <v>46274</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claude</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fehler</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plan und Kauf</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das Berechtigungsmodell wird an keiner einzigen Stelle abgefragt</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">darf() und grenze() aus plan.ts haben im ganzen src/ keinen Aufrufer; nachgesehen mit grep. Nur stempelPlan() läuft, im StoreProvider. Es gibt also heute keine Grenze, die greift, auch nicht für «gratis».</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liste anlegen, Wort anlegen, Teilen, Import fragen darf() und zeigen sonst den Upgrade-Hinweis. Ein Aufrufer je Handgriff, nicht verstreute Abfragen von settings.plan.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alle</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Schwer</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vor Release</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bestätigt</t>
+        </is>
+      </c>
       <c r="M11" s="3"/>
-      <c r="N11" s="2"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Der Kommentar in plan.ts sagt «die Oberfläche fragt darf(...)» — sie tut es noch nicht.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="str">
         <f>IF($F12="","","SV-"&amp;TEXT(ROW()-1,"000"))</f>
-        <v/>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
+        <v>SV-011</v>
+      </c>
+      <c r="B12" s="4">
+        <v>46274</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martin</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aufgabe</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plan und Kauf</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In-App-Kauf «SmartVoc Pro» samt Wiederherstellen bauen</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Weder StoreKit noch ein Capacitor-Kauf-Plugin liegt im Projekt, und in App Store Connect ist kein Produkt angelegt.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nicht verbrauchbarer Kauf, einmalig, kein Abo. Dazu ein sichtbarer Knopf «Käufe wiederherstellen» — Apple verlangt ihn bei nicht verbrauchbaren Käufen (Richtlinie 3.1.1), sonst wird die App abgelehnt.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">iOS</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blocker</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vor Release</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neu</t>
+        </is>
+      </c>
       <c r="M12" s="3"/>
-      <c r="N12" s="2"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zielpreis CHF 6 bis 10, endgültig später. Prüfen: Apple verlangt für den Kauf keinen Account in der App — der Kauf hängt an der Apple-ID, nicht am SmartVoc-Konto.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="str">
         <f>IF($F13="","","SV-"&amp;TEXT(ROW()-1,"000"))</f>
-        <v/>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
+        <v>SV-012</v>
+      </c>
+      <c r="B13" s="4">
+        <v>46274</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claude</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aufgabe</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plan und Kauf</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Entscheidungspunkt: Wie gilt Pro in der Webfassung?</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ein Kauf über Apple lässt sich ohne eigenen Server nicht in der Webfassung prüfen. Das Projekt hat bewusst keinen eigenen Server (Beschränkung C2); Supabase speichert nur Dokumente.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Einen der Wege wählen: die Webfassung bleibt ganz frei; oder der Anspruch wird in der Kontozeile bei Supabase vermerkt und vom Gerät nach dem Kauf gesetzt; oder Pro gilt nur dort, wo gekauft wurde.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Web</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mittel</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vor Release</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neu</t>
+        </is>
+      </c>
       <c r="M13" s="3"/>
-      <c r="N13" s="2"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Der mittlere Weg ist der einzige, der ohne Konto nicht funktioniert — das wäre eine neue Kopplung Kauf an Konto.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="str">
         <f>IF($F14="","","SV-"&amp;TEXT(ROW()-1,"000"))</f>
-        <v/>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
+        <v>SV-013</v>
+      </c>
+      <c r="B14" s="4">
+        <v>46274</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claude</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aufgabe</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teilen</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Entscheidungspunkt: Zählen empfangene Listen gegen die Gratis-Grenze?</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Empfangen läuft heute ohne Konto — get_shared_list ist in schema.sql ausdrücklich an anon vergeben — und importPlan legt eine echte eigene Kopie mit eigenen Wort-Kennungen an. Mit «eine persönliche Liste insgesamt» wäre die zweite empfangene Liste blockiert.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Entscheiden, bevor die Grenze scharf gestellt wird. Drei Wege, keiner davon heute gebaut: eigenes Kontingent für empfangene Listen; empfangene Listen zählen nur gegen die Wortzahl; empfangene Listen bleiben bis zum Kauf nur lesbar.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alle</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Schwer</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vor Release</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neu</t>
+        </is>
+      </c>
       <c r="M14" s="3"/>
-      <c r="N14" s="2"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das ist der Widerspruch im Vorschlag: dieselbe Grenze, die zahlen lassen soll, schneidet den Verbreitungsweg ab, über den die App wachsen soll. Nicht implementieren, bevor entschieden ist.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="str">
         <f>IF($F15="","","SV-"&amp;TEXT(ROW()-1,"000"))</f>
-        <v/>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
+        <v>SV-014</v>
+      </c>
+      <c r="B15" s="4">
+        <v>46274</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claude</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Import und Export</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Empfehlung gegen die Vorlage: Exportieren bleibt frei, nur der Import wird Pro</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Der Vorschlag stellt Import UND Export hinter die Bezahlschranke. In WordList.tsx steht die gegenteilige Entscheidung ausdrücklich im Code: die eigenen Wörter aus der eigenen App zu bringen habe mit einem Konto nichts zu tun.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Export als Text, Excel und PDF bleibt in der Gratis-Fassung. Der Masseneinlese-Weg (Excel/CSV) darf Pro sein.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alle</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mittel</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vor Release</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neu</t>
+        </is>
+      </c>
       <c r="M15" s="3"/>
-      <c r="N15" s="2"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wer seine eigenen Daten nur gegen Geld herausbekommt, hat ein Auskunfts- und Übertragbarkeitsproblem, und in Bewertungen liest es sich schlecht. Empfehlung, kein Einwand gegen den Rest.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="str">
         <f>IF($F16="","","SV-"&amp;TEXT(ROW()-1,"000"))</f>
-        <v/>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
+        <v>SV-015</v>
+      </c>
+      <c r="B16" s="4">
+        <v>46274</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claude</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aufgabe</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plan und Kauf</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50 Wörter: je Liste oder insgesamt?</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRENZEN kennt heute woerterJeListe, und darf(settings, 'wortAnlegen', zahl) bekommt die Zahl vom Aufrufer. Ob 50 pro Liste oder 50 über alles gemeint ist, entscheidet damit heute die Oberfläche, nicht das Modell.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Festlegen und den Feldnamen danach benennen.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alle</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Klein</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vor Release</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neu</t>
+        </is>
+      </c>
       <c r="M16" s="3"/>
-      <c r="N16" s="2"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bei genau einer persönlichen Liste fällt beides zusammen — bis jemand die Liste löscht und eine neue anlegt. Der Grundwortschatz zählt nach heutiger Absicht nicht mit.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="str">
         <f>IF($F17="","","SV-"&amp;TEXT(ROW()-1,"000"))</f>
-        <v/>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
+        <v>SV-016</v>
+      </c>
+      <c r="B17" s="4">
+        <v>46274</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claude</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aufgabe</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plan und Kauf</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bestandsschutz greift — dafür lassen sich die Gratis-Grenzen auf keinem heutigen Gerät testen</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">plan.ts stempelt beim ersten Start «pro» mit Quelle v1 oder bestandsschutz und ändert das nie wieder. Der Mechanismus ist gebaut und tut, was er soll — nachgesehen und in Ordnung.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nebenwirkung bedenken: Jedes Gerät, auf dem die App heute läuft, ist für immer Pro. Zum Prüfen der Gratis-Fassung braucht es eine Neuinstallation nach der Umstellung oder einen Schalter in den Einstellungen.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alle</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mittel</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vor Release</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bestätigt</t>
+        </is>
+      </c>
       <c r="M17" s="3"/>
-      <c r="N17" s="2"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betrifft auch alle TestFlight-Tester. Wenn sie Pro behalten sollen, ist das eine Entscheidung und kein Versehen.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="str">
         <f>IF($F18="","","SV-"&amp;TEXT(ROW()-1,"000"))</f>
-        <v/>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
+        <v>SV-017</v>
+      </c>
+      <c r="B18" s="4">
+        <v>46274</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claude</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aufgabe</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hilfe und Texte</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Texte, die mit einem Kauf falsch werden</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">recht.ts sagt in der Rechtsauskunft wörtlich: «It contains no advertising and no purchases.» In App Store Connect sind keine In-App-Käufe deklariert, und die Store-Beschreibung erwähnt keinen Kauf.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rechtsauskunft, Hilfe, Store-Beschreibung und die Angaben in App Store Connect nachziehen, sobald der Kauf feststeht. Deutsch und Englisch gleichzeitig.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alle</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mittel</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vor Release</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neu</t>
+        </is>
+      </c>
       <c r="M18" s="3"/>
-      <c r="N18" s="2"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Der Satz in recht.ts ist heute wahr und wird mit Pro unwahr. Er steht in einem rechtlichen Text, nicht in Werbung.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="str">
         <f>IF($F19="","","SV-"&amp;TEXT(ROW()-1,"000"))</f>
-        <v/>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
+        <v>SV-018</v>
+      </c>
+      <c r="B19" s="4">
+        <v>46274</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martin</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aufgabe</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Store und Auslieferung</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Release-Prüfliste um die Kaufwege ergänzen</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das bestehende Prüfprotokoll deckt Konto anlegen und löschen, Sync und Konflikte, Sharing, alle sechs Sprachen samt Latein, Zieldatum und Lernplan, Import und Export je Plattform sowie Erststart bereits ab.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neu dazu, weil es das noch nicht gibt: Kauf, Käufe wiederherstellen, Verhalten ohne Netz und bei nicht erreichbarem Store, Verhalten an der Gratis-Grenze, der Upgrade-Weg, und was mit bestehenden lokalen Daten beim Update auf die Fassung mit Grenzen geschieht.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alle</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mittel</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vor Release</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neu</t>
+        </is>
+      </c>
       <c r="M19" s="3"/>
-      <c r="N19" s="2"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kein zweites Dokument anlegen — die übrigen Punkte der Vorlage stehen schon im Prüfprotokoll.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="str">
         <f>IF($F20="","","SV-"&amp;TEXT(ROW()-1,"000"))</f>
-        <v/>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
+        <v>SV-019</v>
+      </c>
+      <c r="B20" s="4">
+        <v>46274</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martin</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aufgabe</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Store und Auslieferung</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vor der Veröffentlichung auf sichtbare Platzhalter und Beta-Reste durchsehen</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nie systematisch durchgegangen.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Einmal durch alle Bereiche, mit Blick auf Reste aus der Entwicklung. Einstellungen → Erweitert zeigt die FSRS-Werte; das ist gewollt und dokumentiert, aber die Entscheidung, ob es öffentlich bleibt, ist nie ausdrücklich gefallen.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alle</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Klein</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vor Release</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neu</t>
+        </is>
+      </c>
       <c r="M20" s="3"/>
       <c r="N20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="str">
         <f>IF($F21="","","SV-"&amp;TEXT(ROW()-1,"000"))</f>
-        <v/>
-      </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
+        <v>SV-020</v>
+      </c>
+      <c r="B21" s="4">
+        <v>46274</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martin</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aufgabe</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sonstiges</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Produktleitlinie festhalten und als Filter für neue Wünsche benutzen</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Die Leitlinie steht bisher nirgends geschrieben.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In die Funktionsspezifikation: Kern sind effizienter Wiederholungsalgorithmus, durchsichtiger Lernstand, prüfungsbezogene Planung und flexible Verwaltung des eigenen Wortschatzes. Kein Sprachkurs, kein soziales Netz, keine Spielereien. Neue Funktionen müssen einen der vier Punkte deutlich verbessern oder das Erfassen und Teilen eigener Listen leichter machen.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Klein</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vor Release</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neu</t>
+        </is>
+      </c>
       <c r="M21" s="3"/>
-      <c r="N21" s="2"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gehört eigentlich in die Spezifikation und nicht ins Fehlerbuch; hier eingetragen, damit sie beim Sichten der Wünsche danebensteht.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="str">
         <f>IF($F22="","","SV-"&amp;TEXT(ROW()-1,"000"))</f>
-        <v/>
-      </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
+        <v>SV-021</v>
+      </c>
+      <c r="B22" s="4">
+        <v>46274</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martin</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wortlisten</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Foto der Buchseite direkt in der App auswerten</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heute der Umweg über eine fremde KI-App: Auftrag kopieren, Foto anhängen, Antwort zurückkopieren.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Foto in SmartVoc aufnehmen oder auswählen, Erkennung und Ergänzung, dann die bestehende Prüfmaske und die Übernahme in eine Liste. Der heutige Weg bleibt daneben bestehen.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alle</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mittel</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nach Release</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neu</t>
+        </is>
+      </c>
       <c r="M22" s="3"/>
-      <c r="N22" s="2"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kritisch vor der Umsetzung: Das braucht einen Dienst, der Bilder auswertet. Damit fällt die Beschränkung «kein eigener Server», und es entstehen Kosten JE Benutzung. Ein einmaliger Kauf von CHF 6 bis 10 trägt keine laufenden Kosten — das Geschäftsmodell muss vorher stimmen. Dazu: neue Angabe «Fotos» im App-Datenschutz und ein Grund für den Kamerazugriff in der Info.plist.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="str">
         <f>IF($F23="","","SV-"&amp;TEXT(ROW()-1,"000"))</f>
-        <v/>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
+        <v>SV-022</v>
+      </c>
+      <c r="B23" s="4">
+        <v>46274</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martin</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Üben</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FSRS-Parameter an die eigene Lernhistorie anpassen</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Feste Werte aus der Literatur, an einer Stelle in fsrs.ts, über Einstellungen → Erweitert einsehbar.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Die Parameter aus dem eigenen Antwortverlauf nachziehen.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alle</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Klein</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nach Release</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neu</t>
+        </is>
+      </c>
       <c r="M23" s="3"/>
-      <c r="N23" s="2"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deine Einschätzung teile ich: gegenüber guten Vorgabewerten ist der Gewinn klein, und er zeigt sich erst nach einigen hundert bis tausend Antworten. Zu bedenken: Die Hilfe verspricht heute ausdrücklich «sie passt das Modell nicht an dich persönlich an und zeichnet dafür auch nichts auf». Der Satz müsste weg, und der App-Datenschutz wäre nochmals anzusehen.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="str">
         <f>IF($F24="","","SV-"&amp;TEXT(ROW()-1,"000"))</f>
-        <v/>
-      </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
+        <v>SV-023</v>
+      </c>
+      <c r="B24" s="4">
+        <v>46274</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martin</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teilen</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teilen zu einem einfachen Klassen-Weg ausbauen</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liste teilen und übernehmen läuft über eine URL; der Empfänger bekommt eine echte Kopie mit eigenem Lernstand — das ist schon so gebaut (importPlan legt jedes Wort neu an).</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liste erstellen, Link oder QR weitergeben, Empfänger übernimmt seine Kopie. Kein soziales Netz, keine Rangliste, keine Freundesliste.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alle</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mittel</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nach Release</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neu</t>
+        </is>
+      </c>
       <c r="M24" s="3"/>
-      <c r="N24" s="2"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Der getrennte Lernstand ist bereits erfüllt. Neu wäre nur der QR-Code — der ist eine URL und passt. Der «Code» aus der Vorlage ist dagegen bewusst abgeschafft worden: du hattest entschieden, nur mit URL zu arbeiten. Nicht wieder einführen.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="str">
         <f>IF($F25="","","SV-"&amp;TEXT(ROW()-1,"000"))</f>
-        <v/>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
+        <v>SV-024</v>
+      </c>
+      <c r="B25" s="4">
+        <v>46274</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martin</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Übungsplan</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prüfungstermin als zentrales Element weiter stärken</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kalender, Ampel, Zieldatum, Tagesportion «Heute dran» und die Prognose je Liste gibt es. Mehrere Listen mit näherem Termin kommen von selbst häufiger dran.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Die vier Fragen — was heute, bin ich auf Kurs, was sitzt schon, wie viel bleibt — an einer Stelle beantworten statt über Reiter verteilt.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alle</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mittel</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nach Release</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neu</t>
+        </is>
+      </c>
       <c r="M25" s="3"/>
-      <c r="N25" s="2"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Der Wunsch ist so noch nicht umsetzbar: Das meiste ist vorhanden. Zuerst benennen, was konkret fehlt, sonst wird daraus eine Umgestaltung ohne Ziel.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="str">
         <f>IF($F26="","","SV-"&amp;TEXT(ROW()-1,"000"))</f>
-        <v/>
-      </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
+        <v>SV-025</v>
+      </c>
+      <c r="B26" s="4">
+        <v>46274</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martin</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Idee</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Konto und Sync</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reduzierte Eltern-Ansicht auf freigegebene Lernpläne</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gibt es nicht.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eltern sehen nur Termine und den zusammengefassten Fortschritt, etwa «Französisch Freitag, auf Kurs, 84 % sitzen, heute rund 12 Wörter». Keine Einsicht in einzelne Wörter oder Fehler.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alle</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Klein</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zurückgestellt</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neu</t>
+        </is>
+      </c>
       <c r="M26" s="3"/>
-      <c r="N26" s="2"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vor der Umsetzung getrennt konzipieren, wie du selbst schreibst. Zu bedenken: Kinderkonten ziehen Apples Kids-Category-Regeln und die Einwilligung der Eltern nach sich. In der Kids Category sind ausgehende Links heikel — die Hilfe verlinkt heute Wikipedia und das FSRS-Projekt. Der App-Datenschutz wäre neu zu fassen.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="str">
@@ -4643,7 +5467,7 @@
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Web-Fassung</t>
+          <t xml:space="preserve">Plan und Kauf</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -4655,16 +5479,22 @@
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Web-Fassung</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kosmetik -- sieht schief aus, funktioniert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Sonstiges</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kosmetik -- sieht schief aus, funktioniert.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+    </row>
     <row r="15">
       <c r="H15" s="6" t="inlineStr">
         <is>
